--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XI/LTAIPT_A63F11.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XI/LTAIPT_A63F11.xlsx
@@ -9,16 +9,18 @@
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_29">Hidden_2!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="79">
   <si>
     <t>48958</t>
   </si>
@@ -86,6 +88,9 @@
     <t>435872</t>
   </si>
   <si>
+    <t>571919</t>
+  </si>
+  <si>
     <t>435873</t>
   </si>
   <si>
@@ -152,6 +157,9 @@
     <t xml:space="preserve">Segundo apellido de la persona contratada </t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Número de contrato</t>
   </si>
   <si>
@@ -164,7 +172,7 @@
     <t>Fecha de término del contrato</t>
   </si>
   <si>
-    <t>Servicios contratados</t>
+    <t>Servicios contratados (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Remuneración mensual bruta o contraprestación</t>
@@ -191,16 +199,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>940C945A0D88107028868C5ED52B9788</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>E09C8CDE9D5BC3C46F52CA33E0E196AF</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Servicios profesionales por honorarios asimilados a salarios</t>
@@ -218,10 +226,13 @@
     <t>Orozco</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Recursos%20Humanos/4to_Trimestre/Contrato/CONTRATO%20JULIO%20CESAR%20PEREZ%20OROZCO%20..pdf</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto%20Recursos%20Humanos/1er%20Trimestre/Julio%20Cesar%202023.pdf</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
   </si>
   <si>
     <t>Asesoría en la reorganización de los procesos informáticos que se ocupan en el Colegio de Bachilleres del Estado de Tlaxcala.</t>
@@ -236,10 +247,16 @@
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>12/01/2023</t>
+    <t>19/04/2023</t>
   </si>
   <si>
     <t>Servicios profesionales por honorarios</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -632,10 +649,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -644,27 +661,28 @@
     <col min="7" max="7" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="155.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="106.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="71.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="97.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="127.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="106.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -681,7 +699,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -696,7 +714,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -722,46 +740,49 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
         <v>6</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>9</v>
-      </c>
-      <c r="L4" t="s">
-        <v>7</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
       </c>
       <c r="N4" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" t="s">
         <v>10</v>
-      </c>
-      <c r="O4" t="s">
-        <v>11</v>
       </c>
       <c r="P4" t="s">
         <v>11</v>
       </c>
       <c r="Q4" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" t="s">
         <v>10</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>9</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>10</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>7</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>12</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -825,10 +846,13 @@
       <c r="V5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -851,143 +875,150 @@
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
-    </row>
-    <row r="7" spans="1:22" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" spans="1:23" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="N8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="S8" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:V6"/>
+    <mergeCell ref="A6:W6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -995,9 +1026,12 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E197">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J201">
+      <formula1>Hidden_29</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1011,12 +1045,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
